--- a/xlsx/tests/calc_tests/WRAPCOLS_ROWS.xlsx
+++ b/xlsx/tests/calc_tests/WRAPCOLS_ROWS.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhatcher/Documents/Excel/LOOKUP_AND_REFERENCE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79191485-5B3B-ED4F-8FCB-C50FC4B5531F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C139EDA-795D-844E-962B-F1C34F15FC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="1580" windowWidth="28040" windowHeight="17180" xr2:uid="{20792D7D-108A-2E48-9E3E-C18D2BEF7AF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D43B4CB-7F1E-D443-BFD9-7965BD62C24E}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -606,6 +606,12 @@
         <v>Warsaw</v>
       </c>
     </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="b" cm="1">
+        <f t="array" ref="A17">_xlfn.WRAPCOLS(IF(1=0, {1,2,3}),2)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
